--- a/data/ratesPerQuantity/File1/RPT_RPT4414865920010NC_ratesPerQuantity.xlsx
+++ b/data/ratesPerQuantity/File1/RPT_RPT4414865920010NC_ratesPerQuantity.xlsx
@@ -35728,7 +35728,7 @@
       </c>
       <c r="D154" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC ELIQUIS</t>
+          <t>NEW GENERIC ELIQUIS</t>
         </is>
       </c>
       <c r="E154" s="49" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="D155" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC ELIQUIS</t>
+          <t>NEW GENERIC ELIQUIS</t>
         </is>
       </c>
       <c r="E155" s="49" t="inlineStr">
@@ -36148,7 +36148,7 @@
       </c>
       <c r="D156" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC ISENTRESS</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="E156" s="49" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="D157" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC IBRANCE</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="E157" s="49" t="inlineStr">
@@ -36572,7 +36572,7 @@
       </c>
       <c r="D158" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC ADVAIR HFA</t>
+          <t>NEW GENERIC ADVAIR HFA</t>
         </is>
       </c>
       <c r="E158" s="49" t="inlineStr">
@@ -36780,7 +36780,7 @@
       </c>
       <c r="D159" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC BREO ELLIPTA</t>
+          <t>NEW GENERIC BREO ELLIPTA</t>
         </is>
       </c>
       <c r="E159" s="49" t="inlineStr">
@@ -36988,7 +36988,7 @@
       </c>
       <c r="D160" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC TRELEGY ELLIPTA</t>
+          <t>NEW GENERIC TRELEGY ELLIPTA</t>
         </is>
       </c>
       <c r="E160" s="49" t="inlineStr">
@@ -37192,7 +37192,7 @@
       </c>
       <c r="D161" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC SYMBICORT</t>
+          <t>NEW GENERIC SYMBICORT</t>
         </is>
       </c>
       <c r="E161" s="49" t="inlineStr">
@@ -37404,7 +37404,7 @@
       </c>
       <c r="D162" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC FARXIGA</t>
+          <t>NEW GENERIC FARXIGA</t>
         </is>
       </c>
       <c r="E162" s="49" t="inlineStr">
@@ -37616,7 +37616,7 @@
       </c>
       <c r="D163" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC FARXIGA</t>
+          <t>NEW GENERIC FARXIGA</t>
         </is>
       </c>
       <c r="E163" s="49" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="D164" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC FARXIGA</t>
+          <t>NEW GENERIC FARXIGA</t>
         </is>
       </c>
       <c r="E164" s="49" t="inlineStr">
@@ -38040,7 +38040,7 @@
       </c>
       <c r="D165" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC XIGDUO XR</t>
+          <t>NEW GENERIC XIGDUO XR</t>
         </is>
       </c>
       <c r="E165" s="49" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="D166" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC BYDUREON BCISE</t>
+          <t>NEW GENERIC BYDUREON BCISE</t>
         </is>
       </c>
       <c r="E166" s="49" t="inlineStr">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="D167" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC AIRSUPRA</t>
+          <t>NEW GENERIC AIRSUPRA</t>
         </is>
       </c>
       <c r="E167" s="49" t="inlineStr">
@@ -38662,7 +38662,7 @@
       </c>
       <c r="D168" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC STIOLTO RESPIMAT</t>
+          <t>NEW GENERIC STIOLTO RESPIMAT</t>
         </is>
       </c>
       <c r="E168" s="49" t="inlineStr">
@@ -38866,7 +38866,7 @@
       </c>
       <c r="D169" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC TIVICAY</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="E169" s="49" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="D170" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC XARELTO</t>
+          <t>NEW GENERIC XARELTO</t>
         </is>
       </c>
       <c r="E170" s="49" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="D171" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC XARELTO</t>
+          <t>NEW GENERIC XARELTO</t>
         </is>
       </c>
       <c r="E171" s="49" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="D172" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC XARELTO</t>
+          <t>NEW GENERIC XARELTO</t>
         </is>
       </c>
       <c r="E172" s="49" t="inlineStr">
@@ -39712,7 +39712,7 @@
       </c>
       <c r="D173" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC XARELTO</t>
+          <t>NEW GENERIC XARELTO</t>
         </is>
       </c>
       <c r="E173" s="49" t="inlineStr">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="D174" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC JAKAFI</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="E174" s="49" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="D175" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC JAKAFI</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="E175" s="49" t="inlineStr">
@@ -40340,7 +40340,7 @@
       </c>
       <c r="D176" s="49" t="inlineStr">
         <is>
-          <t>NEWGENERIC PREZISTA</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="E176" s="49" t="inlineStr">
